--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3386,6 +3386,223 @@
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>129395650</v>
+      </c>
+      <c r="B24" t="n">
+        <v>110623</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Örstig nära skansen, Srm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>622506</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6511364</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ett markkrypande skott, ett klättrande upp i tall. Intill växer några plantor silverarv, vilket kan tyda på att skott av murgröna dumpats här någon gång.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>sandig tallskog</t>
+        </is>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>129395649</v>
+      </c>
+      <c r="B25" t="n">
+        <v>91561</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Örstig nära skansen, Srm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>622410</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6511360</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>sandig tallskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>129395650</v>
       </c>
       <c r="B24" t="n">
-        <v>110623</v>
+        <v>110624</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>129395650</v>
       </c>
       <c r="B24" t="n">
-        <v>110624</v>
+        <v>110628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129395649</v>
       </c>
       <c r="B25" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>129395650</v>
       </c>
       <c r="B24" t="n">
-        <v>110676</v>
+        <v>110688</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129395649</v>
       </c>
       <c r="B25" t="n">
-        <v>91602</v>
+        <v>91608</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>129395650</v>
       </c>
       <c r="B24" t="n">
-        <v>110688</v>
+        <v>110689</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129395649</v>
       </c>
       <c r="B25" t="n">
-        <v>91608</v>
+        <v>91609</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>129395650</v>
       </c>
       <c r="B24" t="n">
-        <v>110689</v>
+        <v>110694</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129395649</v>
       </c>
       <c r="B25" t="n">
-        <v>91609</v>
+        <v>91614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>129395650</v>
       </c>
       <c r="B24" t="n">
-        <v>110694</v>
+        <v>110698</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129395649</v>
       </c>
       <c r="B25" t="n">
-        <v>91614</v>
+        <v>91618</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -3391,7 +3391,7 @@
         <v>129395650</v>
       </c>
       <c r="B24" t="n">
-        <v>110698</v>
+        <v>110700</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3502,7 +3502,7 @@
         <v>129395649</v>
       </c>
       <c r="B25" t="n">
-        <v>91618</v>
+        <v>91620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3603,6 +3603,143 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>130876516</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Örstigsnäs, Strandstuviken, Srm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>622489</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6511356</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Stefan Andersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AY27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3740,6 +3740,125 @@
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132806721</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Andra udden, Andra udden, Srm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>622346</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6511443</v>
+      </c>
+      <c r="S27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-26</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:18</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Ragnar Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Ragnar Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -3745,7 +3745,7 @@
         <v>132806721</v>
       </c>
       <c r="B27" t="n">
-        <v>58439</v>
+        <v>58440</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,60 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>15923646</v>
+        <v>132806721</v>
       </c>
       <c r="B2" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222776</v>
+        <v>103018</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Örstigsnäs ost, Näsudden, Srm</t>
+          <t>Andra udden, Andra udden, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>622456.7827952374</v>
+        <v>622346</v>
       </c>
       <c r="R2" t="n">
-        <v>6511713.013263551</v>
+        <v>6511443</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2014-04-13</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2014-04-13</t>
+          <t>2026-04-26</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>stort bestånd blomning</t>
+          <t>17:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,74 +778,73 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>några m2</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ragnar Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Ragnar Falk</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>15924338</v>
+        <v>97997169</v>
       </c>
       <c r="B3" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>103020</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Örstigsnäs ost, A14, Srm</t>
+          <t>Örstigsnäs, Fågelmatningen, Örstigsnäs gård, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>622456.2970487938</v>
+        <v>622317</v>
       </c>
       <c r="R3" t="n">
-        <v>6511579.984094901</v>
+        <v>6511426</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,22 +868,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,74 +894,73 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Anders Joachimsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Anders Joachimsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>15923620</v>
+        <v>97997170</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Örstigsnäs ost Näsudden, Srm</t>
+          <t>Örstigsnäs, Fågelmatningen, Örstigsnäs gård, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>622357.5075745919</v>
+        <v>622317</v>
       </c>
       <c r="R4" t="n">
-        <v>6511444.36857173</v>
+        <v>6511426</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,27 +984,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-04-13</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-04-13</t>
+          <t>2022-01-09</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ganska vanlig</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,36 +1010,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>öppen mark, glest med björk, hassel mm</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Anders Joachimsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Anders Joachimsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>15924342</v>
+        <v>17182930</v>
       </c>
       <c r="B5" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1052,34 +1037,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>208260</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Örstigsnäs ost, Srm</t>
+          <t>Salstenens brygga, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>622507.8802486341</v>
+        <v>622310</v>
       </c>
       <c r="R5" t="n">
-        <v>6511627.856232245</v>
+        <v>6511674</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1106,22 +1108,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-05-26</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2013-05-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Låg bredvid bryggan och solade sig</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1132,71 +1129,61 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Markus Forsberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15924341</v>
+        <v>61337198</v>
       </c>
       <c r="B6" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>86826</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>2033</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Dvärgfjällskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lepiota echinella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Quél. &amp; G.E. Bernard, 1888</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Örstigsnäs ost, Srm</t>
+          <t>Näsuddens strandstuga, 100 m O om, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>622484.9297027212</v>
+        <v>622365</v>
       </c>
       <c r="R6" t="n">
-        <v>6511645.836705209</v>
+        <v>6511271</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1223,22 +1210,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-09-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>L.echinella s.lat. Belägg sparat mht att arten förmodas vara kollektiv. Biotopen verkar vara intressant - tallskog på mager isälvssand, vilket skiljer den från typen i lundmiljöer.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1252,68 +1234,67 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>tallskog</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>15924339</v>
+        <v>129395649</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Örstigsnäs ost, A14, Srm</t>
+          <t>Örstig nära skansen, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>622476.4128848928</v>
+        <v>622410</v>
       </c>
       <c r="R7" t="n">
-        <v>6511651.802844752</v>
+        <v>6511360</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,27 +1321,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>näst heltäckande 10x10 m2</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1374,71 +1340,82 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>sandig tallskog</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>15944140</v>
+        <v>112579708</v>
       </c>
       <c r="B8" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222776</v>
+        <v>100034</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Örstigsnäs ost, Srm</t>
+          <t>Lilla badplatsen, Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>622462.1509813601</v>
+        <v>622579</v>
       </c>
       <c r="R8" t="n">
-        <v>6511691.360443189</v>
+        <v>6511621</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1462,27 +1439,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-05-11</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-05-11</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>varav 2 hanar</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,36 +1470,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>lövskog, fuktig</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Jan Gustafsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Jan Gustafsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17204072</v>
+        <v>112579720</v>
       </c>
       <c r="B9" t="n">
-        <v>107997</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57903</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1530,42 +1497,53 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219677</v>
+        <v>102110</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Fjällvråk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Buteo lagopus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Pontoppidan, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>sträckande SV</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Örstigsnäs, Srm</t>
+          <t>Lilla badplatsen, Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>622507.8535047541</v>
+        <v>622579</v>
       </c>
       <c r="R9" t="n">
-        <v>6511364.934858898</v>
+        <v>6511621</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1589,27 +1567,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Några slingor</t>
+          <t>ca</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,36 +1598,26 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Blandskog. Gräsmark. Tall och rönn.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Jan Gustafsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Jan Gustafsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>61320362</v>
+        <v>95061567</v>
       </c>
       <c r="B10" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1657,33 +1625,62 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>224363</v>
+        <v>102185</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+          <t>Aromia moschata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Näslandet, 200 m O om båtplatsen, Srm</t>
+          <t>Badplatsen, Örstigsnäs, Srm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>622508.690799289</v>
+        <v>622429</v>
       </c>
       <c r="R10" t="n">
-        <v>6511635.15605698</v>
+        <v>6511333</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1707,22 +1704,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-09-06</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-14</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-09-06</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-07-14</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Räddades ur vattnet vid badplatsen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1731,38 +1723,29 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>barrskog</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Ola Bäckman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Ola Bäckman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>61422209</v>
+        <v>112579687</v>
       </c>
       <c r="B11" t="n">
-        <v>95521</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57947</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1770,33 +1753,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>224363</v>
+        <v>102977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vanlig revlummer</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum subsp. annotinum</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>1K+</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Örstig, strax N om Skansen, Srm</t>
+          <t>Lilla badplatsen, Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>622460.4408220812</v>
+        <v>622579</v>
       </c>
       <c r="R11" t="n">
-        <v>6511580.634484513</v>
+        <v>6511621</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1820,22 +1823,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
+          <t>2023-10-07</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,74 +1849,68 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>granskog</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jan Gustafsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jan Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>61422286</v>
+        <v>133650852</v>
       </c>
       <c r="B12" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58308</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220785</v>
+        <v>103008</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Örstig, alkärr 100 m O om båtbryggan, Srm</t>
+          <t>Skansudden, Srm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>622406.125545503</v>
+        <v>622495</v>
       </c>
       <c r="R12" t="n">
-        <v>6511668.809100442</v>
+        <v>6511486</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1937,22 +1934,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2016-09-15</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1963,36 +1950,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>lövsumpskog</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Per-Ola Björn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Per-Ola Björn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>7250024</v>
+        <v>123730694</v>
       </c>
       <c r="B13" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>60592</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2000,49 +1977,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222776</v>
+        <v>106665</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blåmussla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Mytilus edulis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Örstigsnäs4, Srm</t>
+          <t>Örstigsnäs skans, Srm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>622462.347601519</v>
+        <v>622632</v>
       </c>
       <c r="R13" t="n">
-        <v>6511685.131692225</v>
+        <v>6511457</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2069,27 +2040,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2014-04-05</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Nästan monokultur och heltäckande över stor yta. Både blad och plantor med blomknoppar. Fuktig/våt lövskog m asp mm.</t>
+          <t>2023-04-22</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2098,33 +2054,29 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Amanda Ringqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Amanda Ringqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>17204071</v>
+        <v>132815851</v>
       </c>
       <c r="B14" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>60621</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,42 +2084,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222776</v>
+        <v>106665</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blåmussla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Mytilus edulis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Örstigsnäs, Srm</t>
+          <t>Näsudden badplats, Srm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>622464.4276241303</v>
+        <v>622441</v>
       </c>
       <c r="R14" t="n">
-        <v>6511685.197351895</v>
+        <v>6511335</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2191,22 +2143,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2015-03-16</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2215,81 +2157,72 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Lövskog. Fuktigt område ganska nära havsstrand.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Dennis Nyström, Karin Severin Johansson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>84226237</v>
+        <v>133815562</v>
       </c>
       <c r="B15" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>30293</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222776</v>
+        <v>200985</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Blanksvart trämyra</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Lasius fuliginosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Latreille, 1798)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Örstigsnäs, SO delen., Srm</t>
+          <t>Näsudden badplats, Srm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>622437.9400976734</v>
+        <v>622432</v>
       </c>
       <c r="R15" t="n">
-        <v>6511683.322148422</v>
+        <v>6511380</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2313,27 +2246,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2020-04-04</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2020-04-04</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Stort bestånd. På flera ställen omkring också.</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2342,81 +2260,96 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Sumpskog med björk och asp.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Dennis Nyström, Karin Severin Johansson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>85764748</v>
+        <v>130876516</v>
       </c>
       <c r="B16" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222776</v>
+        <v>208260</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>på övervintringsplats</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Näsudden, Örstigsnäs, Srm</t>
+          <t>Örstigsnäs, Strandstuviken, Srm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>622452.0087507808</v>
+        <v>622489</v>
       </c>
       <c r="R16" t="n">
-        <v>6511699.353561508</v>
+        <v>6511356</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2440,22 +2373,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2020-05-24</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2020-05-24</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2464,38 +2397,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>Sumpig/fuktig lövskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Stefan Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>85764753</v>
+        <v>132815726</v>
       </c>
       <c r="B17" t="n">
-        <v>107845</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2503,16 +2427,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222776</v>
+        <v>219616</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Desmeknopp</t>
+          <t>Ålgräs</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Adoxa moschatellina</t>
+          <t>Zostera marina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2521,24 +2445,23 @@
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Näsudden, Örstigsnäs, Srm</t>
+          <t>Näsudden badplats, Srm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>622457.2415567568</v>
+        <v>622441</v>
       </c>
       <c r="R17" t="n">
-        <v>6511698.47957686</v>
+        <v>6511335</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2562,22 +2485,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2020-05-24</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2020-05-24</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2586,38 +2499,29 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>Sumpig/fuktig lövskog</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Dennis Nyström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jan Yngve Andersson</t>
+          <t>Dennis Nyström, Karin Severin Johansson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>95061567</v>
+        <v>17204072</v>
       </c>
       <c r="B18" t="n">
-        <v>5107</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2625,62 +2529,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102185</v>
+        <v>219677</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Myskbock</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Aromia moschata</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>frispringande/krypande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Badplatsen, Örstigsnäs, Srm</t>
+          <t>Örstigsnäs, Srm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>622428.1795990497</v>
+        <v>622508</v>
       </c>
       <c r="R18" t="n">
-        <v>6511332.801385208</v>
+        <v>6511365</v>
       </c>
       <c r="S18" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2704,27 +2588,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2021-07-14</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-03-16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Räddades ur vattnet vid badplatsen</t>
+          <t>Några slingor</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2733,56 +2607,55 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Blandskog. Gräsmark. Tall och rönn.</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Ola Bäckman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Ola Bäckman</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>97997169</v>
+        <v>71641834</v>
       </c>
       <c r="B19" t="n">
-        <v>56538</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111176</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103020</v>
+        <v>219677</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2790,24 +2663,22 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Örstigsnäs, Fågelmatningen, Örstigsnäs gård, Srm</t>
+          <t>Örstigsnäs NO badet, Srm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>622317.4683111198</v>
+        <v>622507</v>
       </c>
       <c r="R19" t="n">
-        <v>6511426.47847995</v>
+        <v>6511352</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2831,22 +2702,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2018-05-31</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2018-05-31</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Klättrar längs tallstam flera meter upp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2861,74 +2727,64 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anders Joachimsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anders Joachimsson</t>
+          <t>Bjarne Tutturen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>97997170</v>
+        <v>129395650</v>
       </c>
       <c r="B20" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>111175</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>219677</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Örstigsnäs, Fågelmatningen, Örstigsnäs gård, Srm</t>
+          <t>Örstig nära skansen, Srm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>622317.4683111198</v>
+        <v>622506</v>
       </c>
       <c r="R20" t="n">
-        <v>6511426.47847995</v>
+        <v>6511364</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2952,22 +2808,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>12:22</t>
+          <t>2025-10-28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2022-01-09</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>12:41</t>
+          <t>2025-10-28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ett markkrypande skott, ett klättrande upp i tall. Intill växer några plantor silverarv, vilket kan tyda på att skott av murgröna dumpats här någon gång.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2978,85 +2829,69 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>sandig tallskog</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anders Joachimsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anders Joachimsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112579708</v>
+        <v>61422286</v>
       </c>
       <c r="B21" t="n">
-        <v>56524</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100034</v>
+        <v>220785</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blå kärrhök</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Circus cyaneus</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1766)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>1K+</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lilla badplatsen, Näsudden, Srm</t>
+          <t>Örstig, alkärr 100 m O om båtbryggan, Srm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>622580</v>
+        <v>622406</v>
       </c>
       <c r="R21" t="n">
-        <v>6511621</v>
+        <v>6511669</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3080,27 +2915,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>varav 2 hanar</t>
+          <t>2016-09-15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3111,85 +2931,69 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>lövsumpskog</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jan Gustafsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jan Gustafsson</t>
+          <t>Hans Rydberg</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112579720</v>
+        <v>15924338</v>
       </c>
       <c r="B22" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102110</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fjällvråk</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Buteo lagopus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Pontoppidan, 1763)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>1K+</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>sträckande SV</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lilla badplatsen, Näsudden, Srm</t>
+          <t>Örstigsnäs ost, A14, Srm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>622580</v>
+        <v>622456</v>
       </c>
       <c r="R22" t="n">
-        <v>6511621</v>
+        <v>6511580</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3213,27 +3017,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>ca</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3244,31 +3033,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Jan Gustafsson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jan Gustafsson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>112579687</v>
+        <v>15924339</v>
       </c>
       <c r="B23" t="n">
-        <v>56642</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3276,53 +3065,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102977</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>1K+</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lilla badplatsen, Näsudden, Srm</t>
+          <t>Örstigsnäs ost, A14, Srm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>622580</v>
+        <v>622476</v>
       </c>
       <c r="R23" t="n">
-        <v>6511621</v>
+        <v>6511652</v>
       </c>
       <c r="S23" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3346,22 +3119,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-10-07</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>näst heltäckande 10x10 m2</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3372,26 +3140,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jan Gustafsson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jan Gustafsson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129395650</v>
+        <v>15924341</v>
       </c>
       <c r="B24" t="n">
-        <v>110700</v>
+        <v>97983</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3399,16 +3172,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>219677</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3416,21 +3189,17 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Örstig nära skansen, Srm</t>
+          <t>Örstigsnäs ost, Srm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>622506</v>
+        <v>622485</v>
       </c>
       <c r="R24" t="n">
-        <v>6511364</v>
+        <v>6511646</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3457,17 +3226,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ett markkrypande skott, ett klättrande upp i tall. Intill växer några plantor silverarv, vilket kan tyda på att skott av murgröna dumpats här någon gång.</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3481,67 +3245,63 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>sandig tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129395649</v>
+        <v>15924342</v>
       </c>
       <c r="B25" t="n">
-        <v>91620</v>
+        <v>97983</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Örstig nära skansen, Srm</t>
+          <t>Örstigsnäs ost, Srm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>622410</v>
+        <v>622508</v>
       </c>
       <c r="R25" t="n">
-        <v>6511360</v>
+        <v>6511628</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3568,12 +3328,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-10-28</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3587,28 +3347,28 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>sandig tallskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>130876516</v>
+        <v>15923620</v>
       </c>
       <c r="B26" t="n">
-        <v>56836</v>
+        <v>101326</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3616,66 +3376,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>208260</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>på övervintringsplats</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Örstigsnäs, Strandstuviken, Srm</t>
+          <t>Örstigsnäs ost Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>622489</v>
+        <v>622358</v>
       </c>
       <c r="R26" t="n">
-        <v>6511356</v>
+        <v>6511444</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3699,22 +3430,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2014-04-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:00</t>
+          <t>2014-04-13</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ganska vanlig</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3723,29 +3449,33 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>öppen mark, glest med björk, hassel mm</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Stefan Andersson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132806721</v>
+        <v>7250024</v>
       </c>
       <c r="B27" t="n">
-        <v>58444</v>
+        <v>111019</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3753,49 +3483,52 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103018</v>
+        <v>222776</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Andra udden, Andra udden, Srm</t>
+          <t>Örstigsnäs4, Srm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>622346</v>
+        <v>622462</v>
       </c>
       <c r="R27" t="n">
-        <v>6511443</v>
+        <v>6511685</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3819,22 +3552,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>17:18</t>
+          <t>2014-04-05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>17:18</t>
+          <t>2014-04-05</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Nästan monokultur och heltäckande över stor yta. Både blad och plantor med blomknoppar. Fuktig/våt lövskog m asp mm.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3849,22 +3577,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Ragnar Falk</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Ragnar Falk</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133650852</v>
+        <v>15923646</v>
       </c>
       <c r="B28" t="n">
-        <v>58308</v>
+        <v>111019</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3872,41 +3600,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103008</v>
+        <v>222776</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Skansudden, Srm</t>
+          <t>Örstigsnäs ost, Näsudden, Srm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>622495</v>
+        <v>622457</v>
       </c>
       <c r="R28" t="n">
-        <v>6511486</v>
+        <v>6511713</v>
       </c>
       <c r="S28" t="n">
-        <v>150</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3930,12 +3654,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2014-04-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-05-16</t>
+          <t>2014-04-13</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>stort bestånd blomning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3946,69 +3675,69 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>några m2</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Per-Ola Björn</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Per-Ola Björn</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133815562</v>
+        <v>15944140</v>
       </c>
       <c r="B29" t="n">
-        <v>30293</v>
+        <v>111019</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>200985</v>
+        <v>222776</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Blanksvart trämyra</t>
+          <t>Desmeknopp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lasius fuliginosus</t>
+          <t>Adoxa moschatellina</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Latreille, 1798)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Näsudden badplats, Srm</t>
+          <t>Örstigsnäs ost, Srm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>622432</v>
+        <v>622462</v>
       </c>
       <c r="R29" t="n">
-        <v>6511380</v>
+        <v>6511691</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4032,12 +3761,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2014-05-11</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2014-05-11</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4046,22 +3780,655 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>lövskog, fuktig</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Dennis Nyström</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Dennis Nyström, Karin Severin Johansson</t>
+          <t>Jan Yngve Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>17204071</v>
+      </c>
+      <c r="B30" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Örstigsnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>622464</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6511685</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2015-03-16</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2015-03-16</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Lövskog. Fuktigt område ganska nära havsstrand.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>84226237</v>
+      </c>
+      <c r="B31" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Örstigsnäs, SO delen., Srm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>622438</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6511683</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-04-04</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-04-04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Stort bestånd. På flera ställen omkring också.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Sumpskog med björk och asp.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>85764748</v>
+      </c>
+      <c r="B32" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Näsudden, Örstigsnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>622452</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6511699</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-05-24</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-05-24</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Sumpig/fuktig lövskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>85764753</v>
+      </c>
+      <c r="B33" t="n">
+        <v>111019</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>222776</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Desmeknopp</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Adoxa moschatellina</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Näsudden, Örstigsnäs, Srm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>622457</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6511698</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2020-05-24</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2020-05-24</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Sumpig/fuktig lövskog</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jan Yngve Andersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>61320362</v>
+      </c>
+      <c r="B34" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Näslandet, 200 m O om båtplatsen, Srm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>622509</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6511635</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2016-09-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2016-09-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>barrskog</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>61422209</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97985</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>224363</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Vanlig revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum subsp. annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Örstig, strax N om Skansen, Srm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>622460</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6511581</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Nyköping</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2016-09-15</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2016-09-15</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44162-2021 artfynd.xlsx
+++ b/artfynd/A 44162-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY35"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61337198</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129395649</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112579708</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1141,6 +1161,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112579720</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1269,6 +1294,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95061567</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1392,6 +1422,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112579687</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1493,6 +1528,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133650852</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1612,6 +1652,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132806721</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1728,6 +1773,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97997169</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1844,6 +1894,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97997170</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1951,6 +2006,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123730694</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2054,6 +2114,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132815851</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2157,6 +2222,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133815562</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2276,6 +2346,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17182930</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2413,6 +2488,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130876516</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2515,6 +2595,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132815726</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2627,6 +2712,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17204072</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2736,6 +2826,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71641834</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2847,6 +2942,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129395650</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2949,6 +3049,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61422286</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3051,6 +3156,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15924338</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3158,6 +3268,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15924339</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3260,6 +3375,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15924341</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3362,6 +3482,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15924342</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3469,6 +3594,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15923620</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3586,6 +3716,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7250024</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3693,6 +3828,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15923646</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3800,6 +3940,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15944140</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3907,6 +4052,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17204071</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4019,6 +4169,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84226237</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4126,6 +4281,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85764748</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4233,6 +4393,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/85764753</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4331,6 +4496,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61320362</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4429,8 +4599,49 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61422209</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>